--- a/KURIKULUM2026_REVISI/028_DEV_REPORT_DAN_LOG_RESTRUKTURISASI_KODE_CORE_STI.xlsx
+++ b/KURIKULUM2026_REVISI/028_DEV_REPORT_DAN_LOG_RESTRUKTURISASI_KODE_CORE_STI.xlsx
@@ -1739,7 +1739,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>**`STI-624`**</t>
+          <t>**`STI-726`**</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>**`STI-625`**</t>
+          <t>**`STI-727`**</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>**`STI-626`**</t>
+          <t>**`STI-726`**</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>**`STI-627`**</t>
+          <t>**`STI-727`**</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>**`STI-627`**, `MKU-204`</t>
+          <t>**`STI-727`**, `MKU-204`</t>
         </is>
       </c>
     </row>
